--- a/data/valuations/NKE/NKE_modelo_valoracion.xlsx
+++ b/data/valuations/NKE/NKE_modelo_valoracion.xlsx
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.001000000000000001</v>
+        <v>0.011</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.011</v>
+        <v>0.031</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.021</v>
+        <v>0.05</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.031</v>
+        <v>0.05</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.041</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="11">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -983,19 +983,19 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.01506052328934441</v>
+        <v>0.01601857085022818</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.01506052328934441</v>
+        <v>0.01601857085022818</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.01506052328934441</v>
+        <v>0.01601857085022818</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.01506052328934441</v>
+        <v>0.01601857085022818</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.01506052328934441</v>
+        <v>0.01601857085022818</v>
       </c>
     </row>
     <row r="32">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.106</v>
+        <v>0.1074</v>
       </c>
     </row>
     <row r="36">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.096</v>
+        <v>0.0974</v>
       </c>
     </row>
     <row r="37">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.116</v>
+        <v>0.1174</v>
       </c>
     </row>
     <row r="38">
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>52.37</v>
+        <v>51.37</v>
       </c>
     </row>
     <row r="4">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="K21" s="8">
-        <f>K12*$C$16</f>
+        <f>K8*$C$16</f>
         <v/>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/52.37-1</f>
+        <f>C33/51.37-1</f>
         <v/>
       </c>
     </row>
@@ -3753,176 +3753,176 @@
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.076</v>
+        <v>0.0774</v>
       </c>
       <c r="C39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*8/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*8/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*10/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*10/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*12/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*12/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*14/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*14/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*16/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*16/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08739999999999999</v>
       </c>
       <c r="C40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*8/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*8/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*10/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*10/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*12/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*12/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*14/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*14/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*16/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*16/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.096</v>
+        <v>0.0974</v>
       </c>
       <c r="C41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*8/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*8/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*10/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*10/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*12/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*12/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*14/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*14/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*16/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*16/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.106</v>
+        <v>0.1074</v>
       </c>
       <c r="C42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*8/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*8/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*10/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*10/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*12/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*12/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*14/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*14/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*16/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*16/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.116</v>
+        <v>0.1174</v>
       </c>
       <c r="C43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*8/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*8/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*10/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*10/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*12/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*12/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*14/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*14/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*16/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*16/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.126</v>
+        <v>0.1274</v>
       </c>
       <c r="C44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*8/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*8/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*10/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*10/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*12/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*12/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*14/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*14/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*16/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*16/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.136</v>
+        <v>0.1374</v>
       </c>
       <c r="C45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*8/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*8/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*10/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*10/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*12/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*12/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*14/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*14/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*16/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*16/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>

--- a/data/valuations/NKE/NKE_modelo_valoracion.xlsx
+++ b/data/valuations/NKE/NKE_modelo_valoracion.xlsx
@@ -638,19 +638,19 @@
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.0054</v>
+        <v>0.0009000000000000001</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.0048</v>
+        <v>0.0008</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.0042</v>
+        <v>0.0007</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.0036</v>
+        <v>0.0005999999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.021</v>
+        <v>0.016</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.0189</v>
+        <v>0.0144</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.0168</v>
+        <v>0.0128</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.0147</v>
+        <v>0.0112</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.0126</v>
+        <v>0.009599999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -682,13 +682,13 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.011</v>
+        <v>0.006000000000000002</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.031</v>
+        <v>0.026</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.05</v>
+        <v>0.046</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>0.05</v>
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.1074</v>
+        <v>0.1073</v>
       </c>
     </row>
     <row r="36">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.0974</v>
+        <v>0.09730000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.1174</v>
+        <v>0.1173</v>
       </c>
     </row>
     <row r="38">
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>51.37</v>
+        <v>44.19</v>
       </c>
     </row>
     <row r="4">
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/51.37-1</f>
+        <f>C33/44.19-1</f>
         <v/>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.0774</v>
+        <v>0.07730000000000001</v>
       </c>
       <c r="C39" s="22">
         <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*8/(1+$A$39)^5+$C$29)/$C$32</f>
@@ -3778,7 +3778,7 @@
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.08739999999999999</v>
+        <v>0.0873</v>
       </c>
       <c r="C40" s="22">
         <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*8/(1+$A$40)^5+$C$29)/$C$32</f>
@@ -3803,7 +3803,7 @@
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.0974</v>
+        <v>0.09730000000000001</v>
       </c>
       <c r="C41" s="22">
         <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*8/(1+$A$41)^5+$C$29)/$C$32</f>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.1074</v>
+        <v>0.1073</v>
       </c>
       <c r="C42" s="22">
         <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*8/(1+$A$42)^5+$C$29)/$C$32</f>
@@ -3853,7 +3853,7 @@
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.1174</v>
+        <v>0.1173</v>
       </c>
       <c r="C43" s="22">
         <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*8/(1+$A$43)^5+$C$29)/$C$32</f>
@@ -3878,7 +3878,7 @@
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.1274</v>
+        <v>0.1273</v>
       </c>
       <c r="C44" s="22">
         <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*8/(1+$A$44)^5+$C$29)/$C$32</f>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.1374</v>
+        <v>0.1373</v>
       </c>
       <c r="C45" s="22">
         <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*8/(1+$A$45)^5+$C$29)/$C$32</f>
